--- a/strategy_packs/senales_base_senales.xlsx
+++ b/strategy_packs/senales_base_senales.xlsx
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retorno desde el 1º del mes calendario: +10% o más +100, −10% o menos −100. Se reinicia cada mes, así que a principio de mes casi no discrimina.</t>
+          <t>Retorno desde el 1º del mes calendario: +18% o más +100, −13% o menos −100. La escala es asimétrica porque la distribución también lo es, y sale de los percentiles 5 y 95 medidos sobre un mes completo. Dos advertencias: se reinicia cada mes, así que a principio de mes casi no discrimina; y durante el PRIMER mes de cada trimestre (enero, abril, julio y octubre) esta señal y la trimestral miden exactamente lo mismo, porque las dos arrancan en la misma rueda.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"min": -10, "max": 10, "clamp": true}</t>
+          <t>{"min": -13, "max": 18, "clamp": true}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retorno desde el inicio del trimestre calendario: +15% o más +100, −15% o menos −100. También se reinicia, con el mismo efecto al principio del trimestre.</t>
+          <t>Retorno desde el inicio del trimestre calendario: +18% o más +100, −13% o menos −100. También se reinicia, con el mismo efecto al principio del trimestre. Ojo al combinarla con la mensual: durante el primer mes de cada trimestre las dos arrancan en la misma rueda y son el MISMO número, y el resto del tiempo la trimestral contiene a la mensual — usarlas juntas es ponerle doble peso al mismo factor.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"min": -15, "max": 15, "clamp": true}</t>
+          <t>{"min": -13, "max": 18, "clamp": true}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retorno desde el 1º de enero —no los últimos doce meses—: +25% o más +100, −25% o menos −100.</t>
+          <t>Retorno desde el 1º de enero —no los últimos doce meses—: +52% o más +100, −35% o menos −100. La escala sale de los percentiles 5 y 95 medidos con el año ya avanzado; con ±25, que era lo anterior, un tercio de los activos quedaba pegado en ±100 y dejaba de ordenar. Es la que más sufre el reinicio de calendario: en enero casi no discrimina y en diciembre recorta más de lo estimado.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"min": -25, "max": 25, "clamp": true}</t>
+          <t>{"min": -35, "max": 52, "clamp": true}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Retorno de los últimos doce meses, con escala asimétrica porque la distribución también lo es: +80% +100, −20% −100. Es el momentum clásico; para una estrategia de reversión, peso negativo.</t>
+          <t>Retorno de los últimos doce meses, con escala asimétrica porque la distribución también lo es: +85% +100, −38% −100 (percentiles 5 y 95 medidos). La asimetría anterior —−20/+80— estaba inclinada para el lado equivocado y recortaba el doble abajo que arriba. Es el momentum clásico y, a diferencia de los retornos de calendario, su ventana no se reinicia: la escala vale todo el año. Para una estrategia de reversión, peso negativo.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"min": -20, "max": 80, "clamp": true}</t>
+          <t>{"min": -38, "max": 85, "clamp": true}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Volumen de la rueda sobre el promedio de las 20 anteriores: 3 veces lo normal +100, la mitad −100. Cobertura parcial — los sintéticos y las conversiones de moneda no tienen volumen propio y quedan sin puntaje, y una señal sin puntaje NO castiga: se reparten los pesos entre las demás y el activo sin dato termina mejor rankeado. Si la usás, pedí volumen también en el filtro de elegibilidad.</t>
+          <t>Volumen de la rueda sobre el promedio de las 20 anteriores. Los tramos están anclados en la distribución real y son simétricos alrededor de la mediana, así que el puntaje promedio de la señal es cero: el 10% que más opera saca +100 y el 10% que menos, −100. Es a tramos y no lineal porque el ratio tiene cola derecha larguísima (se midió un máximo de 162 contra una mediana de 1) y cualquier escala lineal quedaría dominada por ese extremo. Cobertura parcial — los sintéticos y las conversiones de moneda no tienen volumen propio y quedan sin puntaje, y una señal sin puntaje NO castiga: se reparten los pesos entre las demás y el activo sin dato termina mejor rankeado. Que el promedio sea cero limita ese regalo, pero no lo elimina: si la usás, pedí volumen también en el filtro de elegibilidad.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"min": 0.5, "max": 3, "clamp": true}</t>
+          <t>{"thresholds": [[2.1, 100], [1.3, 60], [1.13, 25], [0.92, 0], [0.76, -25], [0.5, -60], [null, -100]]}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/strategy_packs/senales_base_senales.xlsx
+++ b/strategy_packs/senales_base_senales.xlsx
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retorno desde el inicio del trimestre calendario: +18% o más +100, −13% o menos −100. También se reinicia, con el mismo efecto al principio del trimestre. Ojo al combinarla con la mensual: durante el primer mes de cada trimestre las dos arrancan en la misma rueda y son el MISMO número, y el resto del tiempo la trimestral contiene a la mensual — usarlas juntas es ponerle doble peso al mismo factor.</t>
+          <t>Retorno desde el inicio del trimestre calendario: +44% o más +100, −25% o menos −100. La escala está calibrada sobre un trimestre COMPLETO, que es cuando la dispersión es máxima: medida a mitad de trimestre recorta menos, y eso es lo buscado — comprimir una señal solo le baja el peso efectivo, mientras que recortarla destruye el orden entre los activos que quedan pegados en ±100. Ojo al combinarla con la mensual: durante el primer mes de cada trimestre las dos arrancan en la misma rueda y son el MISMO número, y el resto del tiempo la trimestral contiene a la mensual — usarlas juntas es ponerle doble peso al mismo factor.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"min": -13, "max": 18, "clamp": true}</t>
+          <t>{"min": -25, "max": 44, "clamp": true}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retorno desde el 1º de enero —no los últimos doce meses—: +52% o más +100, −35% o menos −100. La escala sale de los percentiles 5 y 95 medidos con el año ya avanzado; con ±25, que era lo anterior, un tercio de los activos quedaba pegado en ±100 y dejaba de ordenar. Es la que más sufre el reinicio de calendario: en enero casi no discrimina y en diciembre recorta más de lo estimado.</t>
+          <t>Retorno desde el 1º de enero —no los últimos doce meses—: +92% o más +100, −35% o menos −100. Es la señal que más sufre el reinicio de calendario, y la escala está calibrada sobre un año COMPLETO por eso: en enero casi no va a discriminar, que es el costo aceptado. La asimetría no es un gusto: un retorno anual no puede caer de −100% pero no tiene techo para arriba, así que al madurar el año la cola derecha se estira y la izquierda no. Por eso el ajuste va casi todo en el máximo — el mínimo cubre la cola baja más ancha que se midió.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"min": -35, "max": 52, "clamp": true}</t>
+          <t>{"min": -35, "max": 92, "clamp": true}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Volumen de la rueda sobre el promedio de las 20 anteriores. Los tramos están anclados en la distribución real y son simétricos alrededor de la mediana, así que el puntaje promedio de la señal es cero: el 10% que más opera saca +100 y el 10% que menos, −100. Es a tramos y no lineal porque el ratio tiene cola derecha larguísima (se midió un máximo de 162 contra una mediana de 1) y cualquier escala lineal quedaría dominada por ese extremo. Cobertura parcial — los sintéticos y las conversiones de moneda no tienen volumen propio y quedan sin puntaje, y una señal sin puntaje NO castiga: se reparten los pesos entre las demás y el activo sin dato termina mejor rankeado. Que el promedio sea cero limita ese regalo, pero no lo elimina: si la usás, pedí volumen también en el filtro de elegibilidad.</t>
+          <t>Volumen de la rueda sobre el promedio de las 20 anteriores. Los tramos están anclados en la distribución real y son simétricos alrededor de la mediana, así que el puntaje promedio de la señal es cero: los extremos de la distribución sacan +100 y −100, y el 20% central queda en cero. Es a tramos y no lineal porque el ratio tiene cola derecha larguísima (se midió un máximo de 162 contra una mediana de 1) y cualquier escala lineal quedaría dominada por ese extremo. Cobertura parcial — los sintéticos y las conversiones de moneda no tienen volumen propio y quedan sin puntaje, y una señal sin puntaje NO castiga: se reparten los pesos entre las demás y el activo sin dato termina mejor rankeado. Que el promedio sea cero limita ese regalo, pero no lo elimina: si la usás, pedí volumen también en el filtro de elegibilidad.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
